--- a/Assets/Resources/Data/Data.xlsx
+++ b/Assets/Resources/Data/Data.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project_Bin_Unity\Assets\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349FB2D5-4963-4E6B-BCDF-D20AD9B45A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B779B94-43CB-46E8-8E1C-537A2FEAAF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{E9063519-46F7-460A-AC31-718CEBE8B219}"/>
+    <workbookView xWindow="690" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{E9063519-46F7-460A-AC31-718CEBE8B219}"/>
   </bookViews>
   <sheets>
     <sheet name="Dialogue" sheetId="1" r:id="rId1"/>
     <sheet name="Quest" sheetId="2" r:id="rId2"/>
+    <sheet name="Map" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -200,6 +201,62 @@
   </si>
   <si>
     <t>QUEST_COMPLETE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelLimit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImageName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아카데미</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>강릉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>헌터들을 양성하는 헌터 전문 학교, 다양한 수업을 들을 수 있다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>대한민국의 수도</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10년 전 브레이크 당시에 피해가 가장 컸던 지역</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main Menu</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Village</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1446,4 +1503,86 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04537E4-D194-4E31-9314-25663214DAF3}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Resources/Data/Data.xlsx
+++ b/Assets/Resources/Data/Data.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project_Bin_Unity\Assets\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B779B94-43CB-46E8-8E1C-537A2FEAAF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D561D17C-26CE-4B2A-9988-7E4F06823843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{E9063519-46F7-460A-AC31-718CEBE8B219}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E9063519-46F7-460A-AC31-718CEBE8B219}"/>
   </bookViews>
   <sheets>
     <sheet name="Dialogue" sheetId="1" r:id="rId1"/>
     <sheet name="Quest" sheetId="2" r:id="rId2"/>
     <sheet name="Map" sheetId="3" r:id="rId3"/>
+    <sheet name="Tutorial" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -258,6 +259,45 @@
   <si>
     <t>Battle</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>조교</t>
+  </si>
+  <si>
+    <t>신입생 환영회에 온 것을 환영한다.</t>
+  </si>
+  <si>
+    <t>아카데미 입학 처리를 위해 서류를 작성해야 해.</t>
+  </si>
+  <si>
+    <t>자네의 이름은 무엇인가?</t>
+  </si>
+  <si>
+    <t>NAME_INPUT</t>
+  </si>
+  <si>
+    <t>{NAME}? 흐음... 기억해두지.</t>
+  </si>
+  <si>
+    <t>자, 이제 나를 따라와라. 하단의 [스케줄] 버튼을 눌러서 이동할 곳을 확인해.</t>
+  </si>
+  <si>
+    <t>SCHEDULE_GUIDE</t>
+  </si>
+  <si>
+    <t>이곳이 네가 활동할 아카데미의 지도다.</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;[본관]&lt;/color&gt;에서는 수업을 듣거나 동료들과 교류할 수 있다.</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;[운동장]&lt;/color&gt;은 체력 단련이나 실전 훈련을 하는 곳이다.</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;[외출]&lt;/color&gt;을 하면 외부 임무를 수행하거나, 상가로 나갈 수 있다.</t>
   </si>
 </sst>
 </file>
@@ -1585,4 +1625,155 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B42828EB-36E7-4227-A8E7-FA271EED9AA5}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>